--- a/scientisttools/datasets/data/doubs.xlsx
+++ b/scientisttools/datasets/data/doubs.xlsx
@@ -7,10 +7,224 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
+    <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="69">
+  <si>
+    <t>Sites</t>
+  </si>
+  <si>
+    <t>Cogo</t>
+  </si>
+  <si>
+    <t>Satr</t>
+  </si>
+  <si>
+    <t>Phph</t>
+  </si>
+  <si>
+    <t>Neba</t>
+  </si>
+  <si>
+    <t>Thth</t>
+  </si>
+  <si>
+    <t>Teso</t>
+  </si>
+  <si>
+    <t>Chna</t>
+  </si>
+  <si>
+    <t>Chto</t>
+  </si>
+  <si>
+    <t>Lele</t>
+  </si>
+  <si>
+    <t>Lece</t>
+  </si>
+  <si>
+    <t>Baba</t>
+  </si>
+  <si>
+    <t>Spbi</t>
+  </si>
+  <si>
+    <t>Gogo</t>
+  </si>
+  <si>
+    <t>Eslu</t>
+  </si>
+  <si>
+    <t>Pefl</t>
+  </si>
+  <si>
+    <t>Rham</t>
+  </si>
+  <si>
+    <t>Legi</t>
+  </si>
+  <si>
+    <t>Scer</t>
+  </si>
+  <si>
+    <t>Cyca</t>
+  </si>
+  <si>
+    <t>Titi</t>
+  </si>
+  <si>
+    <t>Abbr</t>
+  </si>
+  <si>
+    <t>Icme</t>
+  </si>
+  <si>
+    <t>Acce</t>
+  </si>
+  <si>
+    <t>Ruru</t>
+  </si>
+  <si>
+    <t>Blbj</t>
+  </si>
+  <si>
+    <t>Alal</t>
+  </si>
+  <si>
+    <t>Anan</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>dfs</t>
+  </si>
+  <si>
+    <t>alt</t>
+  </si>
+  <si>
+    <t>slo</t>
+  </si>
+  <si>
+    <t>flo</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>har</t>
+  </si>
+  <si>
+    <t>pho</t>
+  </si>
+  <si>
+    <t>nit</t>
+  </si>
+  <si>
+    <t>amm</t>
+  </si>
+  <si>
+    <t>oxy</t>
+  </si>
+  <si>
+    <t>bdo</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -351,210 +565,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL31"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cogo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Satr</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Phph</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Neba</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Thth</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Teso</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chna</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Chto</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Lele</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Lece</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Baba</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Spbi</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Gogo</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Eslu</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Pefl</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Rham</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Legi</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Scer</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Cyca</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Titi</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Abbr</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Icme</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Acce</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Ruru</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Blbj</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Alal</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Anan</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dfs</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>alt</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>slo</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>flo</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>har</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>pho</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>nit</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>amm</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>oxy</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>bdo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>0</v>
+    <row r="1" spans="1:28" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
+      <c r="A2" t="s">
+        <v>28</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -629,54 +737,3954 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>3</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>4</v>
+      </c>
+      <c r="P6">
+        <v>4</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>2</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>3</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>5</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>5</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>4</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
+      <c r="M18">
+        <v>4</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>2</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>2</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>2</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>3</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>2</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>2</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>2</v>
+      </c>
+      <c r="AB19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>2</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>2</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>5</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>3</v>
+      </c>
+      <c r="AB20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21">
+        <v>4</v>
+      </c>
+      <c r="M21">
+        <v>3</v>
+      </c>
+      <c r="N21">
+        <v>4</v>
+      </c>
+      <c r="O21">
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <v>2</v>
+      </c>
+      <c r="Q21">
+        <v>3</v>
+      </c>
+      <c r="R21">
+        <v>2</v>
+      </c>
+      <c r="S21">
+        <v>2</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>4</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>2</v>
+      </c>
+      <c r="Y21">
+        <v>5</v>
+      </c>
+      <c r="Z21">
+        <v>2</v>
+      </c>
+      <c r="AA21">
+        <v>5</v>
+      </c>
+      <c r="AB21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>4</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22">
+        <v>3</v>
+      </c>
+      <c r="P22">
+        <v>3</v>
+      </c>
+      <c r="Q22">
+        <v>3</v>
+      </c>
+      <c r="R22">
+        <v>2</v>
+      </c>
+      <c r="S22">
+        <v>2</v>
+      </c>
+      <c r="T22">
+        <v>2</v>
+      </c>
+      <c r="U22">
+        <v>4</v>
+      </c>
+      <c r="V22">
+        <v>3</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>3</v>
+      </c>
+      <c r="Y22">
+        <v>5</v>
+      </c>
+      <c r="Z22">
+        <v>3</v>
+      </c>
+      <c r="AA22">
+        <v>5</v>
+      </c>
+      <c r="AB22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <v>5</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>5</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
+      <c r="P23">
+        <v>4</v>
+      </c>
+      <c r="Q23">
+        <v>3</v>
+      </c>
+      <c r="R23">
+        <v>3</v>
+      </c>
+      <c r="S23">
+        <v>2</v>
+      </c>
+      <c r="T23">
+        <v>3</v>
+      </c>
+      <c r="U23">
+        <v>4</v>
+      </c>
+      <c r="V23">
+        <v>4</v>
+      </c>
+      <c r="W23">
+        <v>2</v>
+      </c>
+      <c r="X23">
+        <v>4</v>
+      </c>
+      <c r="Y23">
+        <v>5</v>
+      </c>
+      <c r="Z23">
+        <v>4</v>
+      </c>
+      <c r="AA23">
+        <v>5</v>
+      </c>
+      <c r="AB23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>2</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>2</v>
+      </c>
+      <c r="Y25">
+        <v>2</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>5</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>2</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>1</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>3</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>3</v>
+      </c>
+      <c r="O27">
+        <v>2</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>2</v>
+      </c>
+      <c r="R27">
+        <v>2</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>3</v>
+      </c>
+      <c r="V27">
+        <v>2</v>
+      </c>
+      <c r="W27">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>4</v>
+      </c>
+      <c r="Y27">
+        <v>4</v>
+      </c>
+      <c r="Z27">
+        <v>2</v>
+      </c>
+      <c r="AA27">
+        <v>5</v>
+      </c>
+      <c r="AB27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>3</v>
+      </c>
+      <c r="L28">
+        <v>4</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>4</v>
+      </c>
+      <c r="O28">
+        <v>4</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
+      <c r="R28">
+        <v>3</v>
+      </c>
+      <c r="S28">
+        <v>1</v>
+      </c>
+      <c r="T28">
+        <v>2</v>
+      </c>
+      <c r="U28">
+        <v>5</v>
+      </c>
+      <c r="V28">
+        <v>3</v>
+      </c>
+      <c r="W28">
+        <v>2</v>
+      </c>
+      <c r="X28">
+        <v>5</v>
+      </c>
+      <c r="Y28">
+        <v>5</v>
+      </c>
+      <c r="Z28">
+        <v>4</v>
+      </c>
+      <c r="AA28">
+        <v>5</v>
+      </c>
+      <c r="AB28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>4</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>4</v>
+      </c>
+      <c r="O29">
+        <v>3</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29">
+        <v>4</v>
+      </c>
+      <c r="R29">
+        <v>4</v>
+      </c>
+      <c r="S29">
+        <v>2</v>
+      </c>
+      <c r="T29">
+        <v>4</v>
+      </c>
+      <c r="U29">
+        <v>4</v>
+      </c>
+      <c r="V29">
+        <v>3</v>
+      </c>
+      <c r="W29">
+        <v>3</v>
+      </c>
+      <c r="X29">
+        <v>5</v>
+      </c>
+      <c r="Y29">
+        <v>5</v>
+      </c>
+      <c r="Z29">
+        <v>5</v>
+      </c>
+      <c r="AA29">
+        <v>5</v>
+      </c>
+      <c r="AB29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30">
+        <v>5</v>
+      </c>
+      <c r="M30">
+        <v>3</v>
+      </c>
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30">
+        <v>5</v>
+      </c>
+      <c r="P30">
+        <v>4</v>
+      </c>
+      <c r="Q30">
+        <v>5</v>
+      </c>
+      <c r="R30">
+        <v>5</v>
+      </c>
+      <c r="S30">
+        <v>2</v>
+      </c>
+      <c r="T30">
+        <v>3</v>
+      </c>
+      <c r="U30">
+        <v>3</v>
+      </c>
+      <c r="V30">
+        <v>4</v>
+      </c>
+      <c r="W30">
+        <v>4</v>
+      </c>
+      <c r="X30">
+        <v>5</v>
+      </c>
+      <c r="Y30">
+        <v>5</v>
+      </c>
+      <c r="Z30">
+        <v>4</v>
+      </c>
+      <c r="AA30">
+        <v>5</v>
+      </c>
+      <c r="AB30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31">
+        <v>3</v>
+      </c>
+      <c r="L31">
+        <v>3</v>
+      </c>
+      <c r="M31">
+        <v>5</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31">
+        <v>4</v>
+      </c>
+      <c r="P31">
+        <v>5</v>
+      </c>
+      <c r="Q31">
+        <v>5</v>
+      </c>
+      <c r="R31">
+        <v>3</v>
+      </c>
+      <c r="S31">
+        <v>5</v>
+      </c>
+      <c r="T31">
+        <v>5</v>
+      </c>
+      <c r="U31">
+        <v>5</v>
+      </c>
+      <c r="V31">
+        <v>5</v>
+      </c>
+      <c r="W31">
+        <v>5</v>
+      </c>
+      <c r="X31">
+        <v>5</v>
+      </c>
+      <c r="Y31">
+        <v>5</v>
+      </c>
+      <c r="Z31">
+        <v>5</v>
+      </c>
+      <c r="AA31">
+        <v>5</v>
+      </c>
+      <c r="AB31">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:12" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>934</v>
+      </c>
+      <c r="D2">
+        <v>6.176</v>
+      </c>
+      <c r="E2">
+        <v>84</v>
+      </c>
+      <c r="F2">
+        <v>79</v>
+      </c>
+      <c r="G2">
+        <v>45</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>20</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>122</v>
+      </c>
+      <c r="L2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>932</v>
+      </c>
+      <c r="D3">
+        <v>3.434</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>80</v>
+      </c>
+      <c r="G3">
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>20</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>103</v>
+      </c>
+      <c r="L3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4">
+        <v>102</v>
+      </c>
+      <c r="C4">
+        <v>914</v>
+      </c>
+      <c r="D4">
+        <v>3.638</v>
+      </c>
+      <c r="E4">
+        <v>180</v>
+      </c>
+      <c r="F4">
+        <v>83</v>
+      </c>
+      <c r="G4">
+        <v>52</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>22</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>105</v>
+      </c>
+      <c r="L4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>185</v>
+      </c>
+      <c r="C5">
+        <v>854</v>
+      </c>
+      <c r="D5">
+        <v>3.497</v>
+      </c>
+      <c r="E5">
+        <v>253</v>
+      </c>
+      <c r="F5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>72</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>110</v>
+      </c>
+      <c r="L5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6">
+        <v>215</v>
+      </c>
+      <c r="C6">
+        <v>849</v>
+      </c>
+      <c r="D6">
+        <v>3.178</v>
+      </c>
+      <c r="E6">
+        <v>264</v>
+      </c>
+      <c r="F6">
+        <v>81</v>
+      </c>
+      <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>38</v>
+      </c>
+      <c r="I6">
+        <v>52</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>80</v>
+      </c>
+      <c r="L6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7">
+        <v>324</v>
+      </c>
+      <c r="C7">
+        <v>846</v>
+      </c>
+      <c r="D7">
+        <v>3.497</v>
+      </c>
+      <c r="E7">
+        <v>286</v>
+      </c>
+      <c r="F7">
+        <v>79</v>
+      </c>
+      <c r="G7">
+        <v>60</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>102</v>
+      </c>
+      <c r="L7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8">
+        <v>268</v>
+      </c>
+      <c r="C8">
+        <v>841</v>
+      </c>
+      <c r="D8">
+        <v>4.205</v>
+      </c>
+      <c r="E8">
+        <v>400</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8">
+        <v>88</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>111</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9">
+        <v>491</v>
+      </c>
+      <c r="C9">
+        <v>792</v>
+      </c>
+      <c r="D9">
+        <v>3.258</v>
+      </c>
+      <c r="E9">
+        <v>130</v>
+      </c>
+      <c r="F9">
+        <v>81</v>
+      </c>
+      <c r="G9">
+        <v>94</v>
+      </c>
+      <c r="H9">
+        <v>20</v>
+      </c>
+      <c r="I9">
+        <v>41</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>70</v>
+      </c>
+      <c r="L9">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10">
+        <v>705</v>
+      </c>
+      <c r="C10">
+        <v>752</v>
+      </c>
+      <c r="D10">
+        <v>2.565</v>
+      </c>
+      <c r="E10">
+        <v>480</v>
+      </c>
+      <c r="F10">
+        <v>80</v>
+      </c>
+      <c r="G10">
+        <v>90</v>
+      </c>
+      <c r="H10">
+        <v>30</v>
+      </c>
+      <c r="I10">
+        <v>82</v>
+      </c>
+      <c r="J10">
+        <v>12</v>
+      </c>
+      <c r="K10">
+        <v>72</v>
+      </c>
+      <c r="L10">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11">
+        <v>990</v>
+      </c>
+      <c r="C11">
+        <v>617</v>
+      </c>
+      <c r="D11">
+        <v>4.605</v>
+      </c>
+      <c r="E11">
+        <v>1000</v>
+      </c>
+      <c r="F11">
+        <v>77</v>
+      </c>
+      <c r="G11">
+        <v>82</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>75</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12">
+        <v>1234</v>
+      </c>
+      <c r="C12">
+        <v>483</v>
+      </c>
+      <c r="D12">
+        <v>3.738</v>
+      </c>
+      <c r="E12">
+        <v>1990</v>
+      </c>
+      <c r="F12">
+        <v>81</v>
+      </c>
+      <c r="G12">
+        <v>96</v>
+      </c>
+      <c r="H12">
+        <v>30</v>
+      </c>
+      <c r="I12">
+        <v>160</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>115</v>
+      </c>
+      <c r="L12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13">
+        <v>1324</v>
+      </c>
+      <c r="C13">
+        <v>477</v>
+      </c>
+      <c r="D13">
+        <v>2.833</v>
+      </c>
+      <c r="E13">
+        <v>2000</v>
+      </c>
+      <c r="F13">
+        <v>79</v>
+      </c>
+      <c r="G13">
+        <v>86</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13">
+        <v>50</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>122</v>
+      </c>
+      <c r="L13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14">
+        <v>1436</v>
+      </c>
+      <c r="C14">
+        <v>450</v>
+      </c>
+      <c r="D14">
+        <v>3.091</v>
+      </c>
+      <c r="E14">
+        <v>2110</v>
+      </c>
+      <c r="F14">
+        <v>81</v>
+      </c>
+      <c r="G14">
+        <v>98</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+      <c r="I14">
+        <v>52</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>124</v>
+      </c>
+      <c r="L14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15">
+        <v>1522</v>
+      </c>
+      <c r="C15">
+        <v>434</v>
+      </c>
+      <c r="D15">
+        <v>2.565</v>
+      </c>
+      <c r="E15">
+        <v>2120</v>
+      </c>
+      <c r="F15">
+        <v>83</v>
+      </c>
+      <c r="G15">
+        <v>98</v>
+      </c>
+      <c r="H15">
+        <v>27</v>
+      </c>
+      <c r="I15">
+        <v>123</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>123</v>
+      </c>
+      <c r="L15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16">
+        <v>1645</v>
+      </c>
+      <c r="C16">
+        <v>415</v>
+      </c>
+      <c r="D16">
+        <v>1.792</v>
+      </c>
+      <c r="E16">
+        <v>2300</v>
+      </c>
+      <c r="F16">
+        <v>86</v>
+      </c>
+      <c r="G16">
+        <v>86</v>
+      </c>
+      <c r="H16">
+        <v>40</v>
+      </c>
+      <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>117</v>
+      </c>
+      <c r="L16">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17">
+        <v>1859</v>
+      </c>
+      <c r="C17">
+        <v>375</v>
+      </c>
+      <c r="D17">
+        <v>3.045</v>
+      </c>
+      <c r="E17">
+        <v>1610</v>
+      </c>
+      <c r="F17">
+        <v>80</v>
+      </c>
+      <c r="G17">
+        <v>88</v>
+      </c>
+      <c r="H17">
+        <v>20</v>
+      </c>
+      <c r="I17">
+        <v>200</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+      <c r="K17">
+        <v>103</v>
+      </c>
+      <c r="L17">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18">
+        <v>1985</v>
+      </c>
+      <c r="C18">
+        <v>348</v>
+      </c>
+      <c r="D18">
+        <v>1.792</v>
+      </c>
+      <c r="E18">
+        <v>2430</v>
+      </c>
+      <c r="F18">
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <v>92</v>
+      </c>
+      <c r="H18">
+        <v>20</v>
+      </c>
+      <c r="I18">
+        <v>250</v>
+      </c>
+      <c r="J18">
+        <v>20</v>
+      </c>
+      <c r="K18">
+        <v>102</v>
+      </c>
+      <c r="L18">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19">
+        <v>2110</v>
+      </c>
+      <c r="C19">
+        <v>332</v>
+      </c>
+      <c r="D19">
+        <v>2.197</v>
+      </c>
+      <c r="E19">
+        <v>2500</v>
+      </c>
+      <c r="F19">
+        <v>80</v>
+      </c>
+      <c r="G19">
+        <v>90</v>
+      </c>
+      <c r="H19">
+        <v>50</v>
+      </c>
+      <c r="I19">
+        <v>220</v>
+      </c>
+      <c r="J19">
+        <v>20</v>
+      </c>
+      <c r="K19">
+        <v>103</v>
+      </c>
+      <c r="L19">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20">
+        <v>2246</v>
+      </c>
+      <c r="C20">
+        <v>310</v>
+      </c>
+      <c r="D20">
+        <v>1.792</v>
+      </c>
+      <c r="E20">
+        <v>2590</v>
+      </c>
+      <c r="F20">
+        <v>81</v>
+      </c>
+      <c r="G20">
+        <v>84</v>
+      </c>
+      <c r="H20">
+        <v>60</v>
+      </c>
+      <c r="I20">
+        <v>220</v>
+      </c>
+      <c r="J20">
+        <v>15</v>
+      </c>
+      <c r="K20">
+        <v>106</v>
+      </c>
+      <c r="L20">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21">
+        <v>2477</v>
+      </c>
+      <c r="C21">
+        <v>286</v>
+      </c>
+      <c r="D21">
+        <v>2.197</v>
+      </c>
+      <c r="E21">
+        <v>2680</v>
+      </c>
+      <c r="F21">
+        <v>80</v>
+      </c>
+      <c r="G21">
+        <v>86</v>
+      </c>
+      <c r="H21">
+        <v>30</v>
+      </c>
+      <c r="I21">
+        <v>300</v>
+      </c>
+      <c r="J21">
+        <v>30</v>
+      </c>
+      <c r="K21">
+        <v>103</v>
+      </c>
+      <c r="L21">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22">
+        <v>2812</v>
+      </c>
+      <c r="C22">
+        <v>262</v>
+      </c>
+      <c r="D22">
+        <v>2.398</v>
+      </c>
+      <c r="E22">
+        <v>2720</v>
+      </c>
+      <c r="F22">
+        <v>79</v>
+      </c>
+      <c r="G22">
+        <v>85</v>
+      </c>
+      <c r="H22">
+        <v>20</v>
+      </c>
+      <c r="I22">
+        <v>220</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+      <c r="K22">
+        <v>90</v>
+      </c>
+      <c r="L22">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23">
+        <v>2940</v>
+      </c>
+      <c r="C23">
+        <v>254</v>
+      </c>
+      <c r="D23">
+        <v>2.708</v>
+      </c>
+      <c r="E23">
+        <v>2790</v>
+      </c>
+      <c r="F23">
+        <v>81</v>
+      </c>
+      <c r="G23">
+        <v>88</v>
+      </c>
+      <c r="H23">
+        <v>20</v>
+      </c>
+      <c r="I23">
+        <v>162</v>
+      </c>
+      <c r="J23">
+        <v>7</v>
+      </c>
+      <c r="K23">
+        <v>91</v>
+      </c>
+      <c r="L23">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24">
+        <v>3043</v>
+      </c>
+      <c r="C24">
+        <v>246</v>
+      </c>
+      <c r="D24">
+        <v>2.565</v>
+      </c>
+      <c r="E24">
+        <v>2880</v>
+      </c>
+      <c r="F24">
+        <v>81</v>
+      </c>
+      <c r="G24">
+        <v>97</v>
+      </c>
+      <c r="H24">
+        <v>260</v>
+      </c>
+      <c r="I24">
+        <v>350</v>
+      </c>
+      <c r="J24">
+        <v>115</v>
+      </c>
+      <c r="K24">
+        <v>63</v>
+      </c>
+      <c r="L24">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25">
+        <v>3147</v>
+      </c>
+      <c r="C25">
+        <v>241</v>
+      </c>
+      <c r="D25">
+        <v>1.386</v>
+      </c>
+      <c r="E25">
+        <v>2976</v>
+      </c>
+      <c r="F25">
+        <v>80</v>
+      </c>
+      <c r="G25">
+        <v>99</v>
+      </c>
+      <c r="H25">
+        <v>140</v>
+      </c>
+      <c r="I25">
+        <v>250</v>
+      </c>
+      <c r="J25">
+        <v>60</v>
+      </c>
+      <c r="K25">
+        <v>52</v>
+      </c>
+      <c r="L25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26">
+        <v>3278</v>
+      </c>
+      <c r="C26">
+        <v>231</v>
+      </c>
+      <c r="D26">
+        <v>1.792</v>
+      </c>
+      <c r="E26">
+        <v>3870</v>
+      </c>
+      <c r="F26">
+        <v>79</v>
+      </c>
+      <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26">
+        <v>422</v>
+      </c>
+      <c r="I26">
+        <v>620</v>
+      </c>
+      <c r="J26">
+        <v>180</v>
+      </c>
+      <c r="K26">
+        <v>41</v>
+      </c>
+      <c r="L26">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27">
+        <v>3579</v>
+      </c>
+      <c r="C27">
+        <v>214</v>
+      </c>
+      <c r="D27">
+        <v>1.792</v>
+      </c>
+      <c r="E27">
+        <v>3910</v>
+      </c>
+      <c r="F27">
+        <v>79</v>
+      </c>
+      <c r="G27">
+        <v>94</v>
+      </c>
+      <c r="H27">
+        <v>143</v>
+      </c>
+      <c r="I27">
+        <v>300</v>
+      </c>
+      <c r="J27">
+        <v>30</v>
+      </c>
+      <c r="K27">
+        <v>62</v>
+      </c>
+      <c r="L27">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28">
+        <v>3732</v>
+      </c>
+      <c r="C28">
+        <v>206</v>
+      </c>
+      <c r="D28">
+        <v>2.565</v>
+      </c>
+      <c r="E28">
+        <v>3960</v>
+      </c>
+      <c r="F28">
+        <v>81</v>
+      </c>
+      <c r="G28">
+        <v>90</v>
+      </c>
+      <c r="H28">
+        <v>58</v>
+      </c>
+      <c r="I28">
+        <v>300</v>
+      </c>
+      <c r="J28">
+        <v>26</v>
+      </c>
+      <c r="K28">
+        <v>72</v>
+      </c>
+      <c r="L28">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29">
+        <v>3947</v>
+      </c>
+      <c r="C29">
+        <v>195</v>
+      </c>
+      <c r="D29">
+        <v>1.386</v>
+      </c>
+      <c r="E29">
+        <v>4320</v>
+      </c>
+      <c r="F29">
+        <v>83</v>
+      </c>
+      <c r="G29">
+        <v>100</v>
+      </c>
+      <c r="H29">
+        <v>74</v>
+      </c>
+      <c r="I29">
+        <v>400</v>
+      </c>
+      <c r="J29">
+        <v>30</v>
+      </c>
+      <c r="K29">
+        <v>81</v>
+      </c>
+      <c r="L29">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30">
+        <v>4220</v>
+      </c>
+      <c r="C30">
+        <v>183</v>
+      </c>
+      <c r="D30">
+        <v>1.946</v>
+      </c>
+      <c r="E30">
+        <v>6770</v>
+      </c>
+      <c r="F30">
+        <v>78</v>
+      </c>
+      <c r="G30">
+        <v>110</v>
+      </c>
+      <c r="H30">
+        <v>45</v>
+      </c>
+      <c r="I30">
+        <v>162</v>
+      </c>
+      <c r="J30">
+        <v>10</v>
+      </c>
+      <c r="K30">
+        <v>90</v>
+      </c>
+      <c r="L30">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31">
+        <v>4530</v>
+      </c>
+      <c r="C31">
+        <v>172</v>
+      </c>
+      <c r="D31">
+        <v>1.099</v>
+      </c>
+      <c r="E31">
+        <v>6900</v>
+      </c>
+      <c r="F31">
+        <v>82</v>
+      </c>
+      <c r="G31">
+        <v>109</v>
+      </c>
+      <c r="H31">
+        <v>65</v>
+      </c>
+      <c r="I31">
+        <v>160</v>
+      </c>
+      <c r="J31">
+        <v>10</v>
+      </c>
+      <c r="K31">
+        <v>82</v>
+      </c>
+      <c r="L31">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AM31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:39" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
       </c>
       <c r="AC2">
+        <v>3</v>
+      </c>
+      <c r="AD2">
         <v>934</v>
       </c>
-      <c r="AD2">
+      <c r="AE2">
         <v>6.176</v>
       </c>
-      <c r="AE2">
+      <c r="AF2">
         <v>84</v>
       </c>
-      <c r="AF2">
+      <c r="AG2">
         <v>79</v>
       </c>
-      <c r="AG2">
+      <c r="AH2">
         <v>45</v>
       </c>
-      <c r="AH2">
-        <v>1</v>
-      </c>
       <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
         <v>20</v>
       </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
       <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
         <v>122</v>
       </c>
-      <c r="AL2">
+      <c r="AM2">
         <v>27</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3">
-        <v>0</v>
+    <row r="3" spans="1:39">
+      <c r="A3" t="s">
+        <v>29</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -745,45 +4753,48 @@
         <v>0</v>
       </c>
       <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <v>22</v>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>932</v>
       </c>
-      <c r="AD3">
+      <c r="AE3">
         <v>3.434</v>
       </c>
-      <c r="AE3">
+      <c r="AF3">
         <v>100</v>
       </c>
-      <c r="AF3">
+      <c r="AG3">
         <v>80</v>
       </c>
-      <c r="AG3">
+      <c r="AH3">
         <v>40</v>
       </c>
-      <c r="AH3">
-        <v>2</v>
-      </c>
       <c r="AI3">
+        <v>2</v>
+      </c>
+      <c r="AJ3">
         <v>20</v>
       </c>
-      <c r="AJ3">
+      <c r="AK3">
         <v>10</v>
       </c>
-      <c r="AK3">
+      <c r="AL3">
         <v>103</v>
       </c>
-      <c r="AL3">
+      <c r="AM3">
         <v>19</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4">
-        <v>0</v>
+    <row r="4" spans="1:39">
+      <c r="A4" t="s">
+        <v>30</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -792,7 +4803,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -819,10 +4830,10 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -861,54 +4872,57 @@
         <v>0</v>
       </c>
       <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
         <v>102</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <v>914</v>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <v>3.638</v>
       </c>
-      <c r="AE4">
+      <c r="AF4">
         <v>180</v>
       </c>
-      <c r="AF4">
+      <c r="AG4">
         <v>83</v>
       </c>
-      <c r="AG4">
+      <c r="AH4">
         <v>52</v>
       </c>
-      <c r="AH4">
-        <v>5</v>
-      </c>
       <c r="AI4">
+        <v>5</v>
+      </c>
+      <c r="AJ4">
         <v>22</v>
       </c>
-      <c r="AJ4">
-        <v>5</v>
-      </c>
       <c r="AK4">
+        <v>5</v>
+      </c>
+      <c r="AL4">
         <v>105</v>
       </c>
-      <c r="AL4">
+      <c r="AM4">
         <v>35</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5">
-        <v>0</v>
+    <row r="5" spans="1:39">
+      <c r="A5" t="s">
+        <v>31</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -923,25 +4937,25 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <v>2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -953,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -977,54 +4991,57 @@
         <v>0</v>
       </c>
       <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
         <v>185</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>854</v>
       </c>
-      <c r="AD5">
+      <c r="AE5">
         <v>3.497</v>
       </c>
-      <c r="AE5">
+      <c r="AF5">
         <v>253</v>
       </c>
-      <c r="AF5">
+      <c r="AG5">
         <v>80</v>
       </c>
-      <c r="AG5">
+      <c r="AH5">
         <v>72</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>10</v>
       </c>
-      <c r="AI5">
+      <c r="AJ5">
         <v>21</v>
       </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
       <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
         <v>110</v>
       </c>
-      <c r="AL5">
+      <c r="AM5">
         <v>13</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6">
-        <v>0</v>
+    <row r="6" spans="1:39">
+      <c r="A6" t="s">
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1036,43 +5053,43 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O6">
         <v>4</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1081,10 +5098,10 @@
         <v>0</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1093,54 +5110,57 @@
         <v>0</v>
       </c>
       <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
         <v>215</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <v>849</v>
       </c>
-      <c r="AD6">
+      <c r="AE6">
         <v>3.178</v>
       </c>
-      <c r="AE6">
+      <c r="AF6">
         <v>264</v>
       </c>
-      <c r="AF6">
+      <c r="AG6">
         <v>81</v>
       </c>
-      <c r="AG6">
+      <c r="AH6">
         <v>84</v>
       </c>
-      <c r="AH6">
+      <c r="AI6">
         <v>38</v>
       </c>
-      <c r="AI6">
+      <c r="AJ6">
         <v>52</v>
       </c>
-      <c r="AJ6">
+      <c r="AK6">
         <v>20</v>
       </c>
-      <c r="AK6">
+      <c r="AL6">
         <v>80</v>
       </c>
-      <c r="AL6">
+      <c r="AM6">
         <v>62</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7">
-        <v>0</v>
+    <row r="7" spans="1:39">
+      <c r="A7" t="s">
+        <v>33</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1152,19 +5172,19 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -1173,7 +5193,7 @@
         <v>1</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1185,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -1197,10 +5217,10 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1209,54 +5229,57 @@
         <v>0</v>
       </c>
       <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
         <v>324</v>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <v>846</v>
       </c>
-      <c r="AD7">
+      <c r="AE7">
         <v>3.497</v>
       </c>
-      <c r="AE7">
+      <c r="AF7">
         <v>286</v>
       </c>
-      <c r="AF7">
+      <c r="AG7">
         <v>79</v>
       </c>
-      <c r="AG7">
+      <c r="AH7">
         <v>60</v>
       </c>
-      <c r="AH7">
+      <c r="AI7">
         <v>20</v>
       </c>
-      <c r="AI7">
+      <c r="AJ7">
         <v>15</v>
       </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
       <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
         <v>102</v>
       </c>
-      <c r="AL7">
+      <c r="AM7">
         <v>53</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8">
-        <v>0</v>
+    <row r="8" spans="1:39">
+      <c r="A8" t="s">
+        <v>34</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1268,13 +5291,13 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1325,42 +5348,45 @@
         <v>0</v>
       </c>
       <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
         <v>268</v>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <v>841</v>
       </c>
-      <c r="AD8">
+      <c r="AE8">
         <v>4.205</v>
       </c>
-      <c r="AE8">
+      <c r="AF8">
         <v>400</v>
       </c>
-      <c r="AF8">
+      <c r="AG8">
         <v>81</v>
       </c>
-      <c r="AG8">
+      <c r="AH8">
         <v>88</v>
       </c>
-      <c r="AH8">
+      <c r="AI8">
         <v>7</v>
       </c>
-      <c r="AI8">
+      <c r="AJ8">
         <v>15</v>
       </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
       <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
         <v>111</v>
       </c>
-      <c r="AL8">
+      <c r="AM8">
         <v>22</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9">
-        <v>0</v>
+    <row r="9" spans="1:39">
+      <c r="A9" t="s">
+        <v>35</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1441,54 +5467,57 @@
         <v>0</v>
       </c>
       <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
         <v>491</v>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <v>792</v>
       </c>
-      <c r="AD9">
+      <c r="AE9">
         <v>3.258</v>
       </c>
-      <c r="AE9">
+      <c r="AF9">
         <v>130</v>
       </c>
-      <c r="AF9">
+      <c r="AG9">
         <v>81</v>
       </c>
-      <c r="AG9">
+      <c r="AH9">
         <v>94</v>
       </c>
-      <c r="AH9">
+      <c r="AI9">
         <v>20</v>
       </c>
-      <c r="AI9">
+      <c r="AJ9">
         <v>41</v>
       </c>
-      <c r="AJ9">
+      <c r="AK9">
         <v>12</v>
       </c>
-      <c r="AK9">
+      <c r="AL9">
         <v>70</v>
       </c>
-      <c r="AL9">
+      <c r="AM9">
         <v>81</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10">
-        <v>0</v>
+    <row r="10" spans="1:39">
+      <c r="A10" t="s">
+        <v>36</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1503,10 +5532,10 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1533,10 +5562,10 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -1545,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -1557,54 +5586,57 @@
         <v>0</v>
       </c>
       <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
         <v>705</v>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <v>752</v>
       </c>
-      <c r="AD10">
+      <c r="AE10">
         <v>2.565</v>
       </c>
-      <c r="AE10">
+      <c r="AF10">
         <v>480</v>
       </c>
-      <c r="AF10">
+      <c r="AG10">
         <v>80</v>
       </c>
-      <c r="AG10">
+      <c r="AH10">
         <v>90</v>
       </c>
-      <c r="AH10">
+      <c r="AI10">
         <v>30</v>
       </c>
-      <c r="AI10">
+      <c r="AJ10">
         <v>82</v>
       </c>
-      <c r="AJ10">
+      <c r="AK10">
         <v>12</v>
       </c>
-      <c r="AK10">
+      <c r="AL10">
         <v>72</v>
       </c>
-      <c r="AL10">
+      <c r="AM10">
         <v>52</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11">
-        <v>0</v>
+    <row r="11" spans="1:39">
+      <c r="A11" t="s">
+        <v>37</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1616,22 +5648,22 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>2</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1673,57 +5705,60 @@
         <v>0</v>
       </c>
       <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
         <v>990</v>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <v>617</v>
       </c>
-      <c r="AD11">
+      <c r="AE11">
         <v>4.605</v>
       </c>
-      <c r="AE11">
+      <c r="AF11">
         <v>1000</v>
       </c>
-      <c r="AF11">
+      <c r="AG11">
         <v>77</v>
       </c>
-      <c r="AG11">
+      <c r="AH11">
         <v>82</v>
       </c>
-      <c r="AH11">
+      <c r="AI11">
         <v>6</v>
       </c>
-      <c r="AI11">
+      <c r="AJ11">
         <v>75</v>
       </c>
-      <c r="AJ11">
-        <v>1</v>
-      </c>
       <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
         <v>100</v>
       </c>
-      <c r="AL11">
+      <c r="AM11">
         <v>43</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12">
-        <v>1</v>
+    <row r="12" spans="1:39">
+      <c r="A12" t="s">
+        <v>38</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1735,10 +5770,10 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1789,57 +5824,60 @@
         <v>0</v>
       </c>
       <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
         <v>1234</v>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <v>483</v>
       </c>
-      <c r="AD12">
+      <c r="AE12">
         <v>3.738</v>
       </c>
-      <c r="AE12">
+      <c r="AF12">
         <v>1990</v>
       </c>
-      <c r="AF12">
+      <c r="AG12">
         <v>81</v>
       </c>
-      <c r="AG12">
+      <c r="AH12">
         <v>96</v>
       </c>
-      <c r="AH12">
+      <c r="AI12">
         <v>30</v>
       </c>
-      <c r="AI12">
+      <c r="AJ12">
         <v>160</v>
       </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
       <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
         <v>115</v>
       </c>
-      <c r="AL12">
+      <c r="AM12">
         <v>27</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13">
-        <v>2</v>
+    <row r="13" spans="1:39">
+      <c r="A13" t="s">
+        <v>39</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1851,10 +5889,10 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1905,60 +5943,63 @@
         <v>0</v>
       </c>
       <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
         <v>1324</v>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <v>477</v>
       </c>
-      <c r="AD13">
+      <c r="AE13">
         <v>2.833</v>
       </c>
-      <c r="AE13">
+      <c r="AF13">
         <v>2000</v>
       </c>
-      <c r="AF13">
+      <c r="AG13">
         <v>79</v>
       </c>
-      <c r="AG13">
+      <c r="AH13">
         <v>86</v>
       </c>
-      <c r="AH13">
-        <v>4</v>
-      </c>
       <c r="AI13">
+        <v>4</v>
+      </c>
+      <c r="AJ13">
         <v>50</v>
       </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
       <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
         <v>122</v>
       </c>
-      <c r="AL13">
+      <c r="AM13">
         <v>30</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14">
-        <v>2</v>
+    <row r="14" spans="1:39">
+      <c r="A14" t="s">
+        <v>40</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C14">
         <v>5</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2021,60 +6062,63 @@
         <v>0</v>
       </c>
       <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
         <v>1436</v>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <v>450</v>
       </c>
-      <c r="AD14">
+      <c r="AE14">
         <v>3.091</v>
       </c>
-      <c r="AE14">
+      <c r="AF14">
         <v>2110</v>
       </c>
-      <c r="AF14">
+      <c r="AG14">
         <v>81</v>
       </c>
-      <c r="AG14">
+      <c r="AH14">
         <v>98</v>
       </c>
-      <c r="AH14">
+      <c r="AI14">
         <v>6</v>
       </c>
-      <c r="AI14">
+      <c r="AJ14">
         <v>52</v>
       </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
       <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
         <v>124</v>
       </c>
-      <c r="AL14">
+      <c r="AM14">
         <v>24</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15">
-        <v>3</v>
+    <row r="15" spans="1:39">
+      <c r="A15" t="s">
+        <v>41</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2083,22 +6127,22 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2137,81 +6181,84 @@
         <v>0</v>
       </c>
       <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
         <v>1522</v>
       </c>
-      <c r="AC15">
+      <c r="AD15">
         <v>434</v>
       </c>
-      <c r="AD15">
+      <c r="AE15">
         <v>2.565</v>
       </c>
-      <c r="AE15">
+      <c r="AF15">
         <v>2120</v>
       </c>
-      <c r="AF15">
+      <c r="AG15">
         <v>83</v>
       </c>
-      <c r="AG15">
+      <c r="AH15">
         <v>98</v>
       </c>
-      <c r="AH15">
+      <c r="AI15">
         <v>27</v>
       </c>
-      <c r="AI15">
+      <c r="AJ15">
         <v>123</v>
       </c>
-      <c r="AJ15">
-        <v>0</v>
-      </c>
       <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
         <v>123</v>
       </c>
-      <c r="AL15">
+      <c r="AM15">
         <v>38</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16">
-        <v>3</v>
+    <row r="16" spans="1:39">
+      <c r="A16" t="s">
+        <v>42</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>4</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>3</v>
       </c>
       <c r="K16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -2229,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -2253,102 +6300,105 @@
         <v>0</v>
       </c>
       <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
         <v>1645</v>
       </c>
-      <c r="AC16">
+      <c r="AD16">
         <v>415</v>
       </c>
-      <c r="AD16">
+      <c r="AE16">
         <v>1.792</v>
       </c>
-      <c r="AE16">
+      <c r="AF16">
         <v>2300</v>
-      </c>
-      <c r="AF16">
-        <v>86</v>
       </c>
       <c r="AG16">
         <v>86</v>
       </c>
       <c r="AH16">
+        <v>86</v>
+      </c>
+      <c r="AI16">
         <v>40</v>
       </c>
-      <c r="AI16">
+      <c r="AJ16">
         <v>100</v>
       </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
       <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
         <v>117</v>
       </c>
-      <c r="AL16">
+      <c r="AM16">
         <v>21</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17">
-        <v>2</v>
+    <row r="17" spans="1:39">
+      <c r="A17" t="s">
+        <v>43</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>2</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17">
         <v>1</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17">
         <v>1</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -2357,10 +6407,10 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2369,102 +6419,105 @@
         <v>0</v>
       </c>
       <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
         <v>1859</v>
       </c>
-      <c r="AC17">
+      <c r="AD17">
         <v>375</v>
       </c>
-      <c r="AD17">
+      <c r="AE17">
         <v>3.045</v>
       </c>
-      <c r="AE17">
+      <c r="AF17">
         <v>1610</v>
       </c>
-      <c r="AF17">
+      <c r="AG17">
         <v>80</v>
       </c>
-      <c r="AG17">
+      <c r="AH17">
         <v>88</v>
       </c>
-      <c r="AH17">
+      <c r="AI17">
         <v>20</v>
       </c>
-      <c r="AI17">
+      <c r="AJ17">
         <v>200</v>
       </c>
-      <c r="AJ17">
-        <v>5</v>
-      </c>
       <c r="AK17">
+        <v>5</v>
+      </c>
+      <c r="AL17">
         <v>103</v>
       </c>
-      <c r="AL17">
+      <c r="AM17">
         <v>27</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18">
-        <v>1</v>
+    <row r="18" spans="1:39">
+      <c r="A18" t="s">
+        <v>44</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N18">
         <v>1</v>
       </c>
       <c r="O18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18">
         <v>1</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18">
         <v>1</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -2473,66 +6526,69 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
         <v>1985</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>348</v>
       </c>
-      <c r="AD18">
+      <c r="AE18">
         <v>1.792</v>
       </c>
-      <c r="AE18">
+      <c r="AF18">
         <v>2430</v>
       </c>
-      <c r="AF18">
+      <c r="AG18">
         <v>80</v>
       </c>
-      <c r="AG18">
+      <c r="AH18">
         <v>92</v>
       </c>
-      <c r="AH18">
+      <c r="AI18">
         <v>20</v>
       </c>
-      <c r="AI18">
+      <c r="AJ18">
         <v>250</v>
       </c>
-      <c r="AJ18">
+      <c r="AK18">
         <v>20</v>
       </c>
-      <c r="AK18">
+      <c r="AL18">
         <v>102</v>
       </c>
-      <c r="AL18">
+      <c r="AM18">
         <v>46</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19">
-        <v>1</v>
+    <row r="19" spans="1:39">
+      <c r="A19" t="s">
+        <v>45</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2541,13 +6597,13 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19">
         <v>3</v>
@@ -2556,135 +6612,138 @@
         <v>3</v>
       </c>
       <c r="M19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19">
         <v>1</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB19">
+        <v>1</v>
+      </c>
+      <c r="AC19">
         <v>2110</v>
       </c>
-      <c r="AC19">
+      <c r="AD19">
         <v>332</v>
       </c>
-      <c r="AD19">
+      <c r="AE19">
         <v>2.197</v>
       </c>
-      <c r="AE19">
+      <c r="AF19">
         <v>2500</v>
       </c>
-      <c r="AF19">
+      <c r="AG19">
         <v>80</v>
       </c>
-      <c r="AG19">
+      <c r="AH19">
         <v>90</v>
       </c>
-      <c r="AH19">
+      <c r="AI19">
         <v>50</v>
       </c>
-      <c r="AI19">
+      <c r="AJ19">
         <v>220</v>
       </c>
-      <c r="AJ19">
+      <c r="AK19">
         <v>20</v>
       </c>
-      <c r="AK19">
+      <c r="AL19">
         <v>103</v>
       </c>
-      <c r="AL19">
+      <c r="AM19">
         <v>28</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20">
-        <v>0</v>
+    <row r="20" spans="1:39">
+      <c r="A20" t="s">
+        <v>46</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <v>2</v>
       </c>
       <c r="M20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>1</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -2693,84 +6752,87 @@
         <v>1</v>
       </c>
       <c r="T20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
         <v>2246</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>310</v>
       </c>
-      <c r="AD20">
+      <c r="AE20">
         <v>1.792</v>
       </c>
-      <c r="AE20">
+      <c r="AF20">
         <v>2590</v>
       </c>
-      <c r="AF20">
+      <c r="AG20">
         <v>81</v>
       </c>
-      <c r="AG20">
+      <c r="AH20">
         <v>84</v>
       </c>
-      <c r="AH20">
+      <c r="AI20">
         <v>60</v>
       </c>
-      <c r="AI20">
+      <c r="AJ20">
         <v>220</v>
       </c>
-      <c r="AJ20">
+      <c r="AK20">
         <v>15</v>
       </c>
-      <c r="AK20">
+      <c r="AL20">
         <v>106</v>
       </c>
-      <c r="AL20">
+      <c r="AM20">
         <v>33</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21">
-        <v>0</v>
+    <row r="21" spans="1:39">
+      <c r="A21" t="s">
+        <v>47</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>2</v>
@@ -2779,114 +6841,117 @@
         <v>2</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O21">
         <v>2</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R21">
         <v>2</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB21">
+        <v>2</v>
+      </c>
+      <c r="AC21">
         <v>2477</v>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <v>286</v>
       </c>
-      <c r="AD21">
+      <c r="AE21">
         <v>2.197</v>
       </c>
-      <c r="AE21">
+      <c r="AF21">
         <v>2680</v>
       </c>
-      <c r="AF21">
+      <c r="AG21">
         <v>80</v>
       </c>
-      <c r="AG21">
+      <c r="AH21">
         <v>86</v>
       </c>
-      <c r="AH21">
+      <c r="AI21">
         <v>30</v>
       </c>
-      <c r="AI21">
+      <c r="AJ21">
         <v>300</v>
       </c>
-      <c r="AJ21">
+      <c r="AK21">
         <v>30</v>
       </c>
-      <c r="AK21">
+      <c r="AL21">
         <v>103</v>
       </c>
-      <c r="AL21">
+      <c r="AM21">
         <v>28</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22">
-        <v>0</v>
+    <row r="22" spans="1:39">
+      <c r="A22" t="s">
+        <v>48</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>2</v>
@@ -2898,16 +6963,16 @@
         <v>2</v>
       </c>
       <c r="K22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>3</v>
@@ -2916,7 +6981,7 @@
         <v>3</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R22">
         <v>2</v>
@@ -2925,66 +6990,69 @@
         <v>2</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y22">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB22">
+        <v>2</v>
+      </c>
+      <c r="AC22">
         <v>2812</v>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <v>262</v>
       </c>
-      <c r="AD22">
+      <c r="AE22">
         <v>2.398</v>
       </c>
-      <c r="AE22">
+      <c r="AF22">
         <v>2720</v>
       </c>
-      <c r="AF22">
+      <c r="AG22">
         <v>79</v>
       </c>
-      <c r="AG22">
+      <c r="AH22">
         <v>85</v>
       </c>
-      <c r="AH22">
+      <c r="AI22">
         <v>20</v>
       </c>
-      <c r="AI22">
+      <c r="AJ22">
         <v>220</v>
       </c>
-      <c r="AJ22">
+      <c r="AK22">
         <v>10</v>
       </c>
-      <c r="AK22">
+      <c r="AL22">
         <v>90</v>
       </c>
-      <c r="AL22">
+      <c r="AM22">
         <v>41</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23">
-        <v>0</v>
+    <row r="23" spans="1:39">
+      <c r="A23" t="s">
+        <v>49</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2993,114 +7061,117 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q23">
         <v>3</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U23">
         <v>4</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB23">
+        <v>2</v>
+      </c>
+      <c r="AC23">
         <v>2940</v>
       </c>
-      <c r="AC23">
+      <c r="AD23">
         <v>254</v>
       </c>
-      <c r="AD23">
+      <c r="AE23">
         <v>2.708</v>
       </c>
-      <c r="AE23">
+      <c r="AF23">
         <v>2790</v>
       </c>
-      <c r="AF23">
+      <c r="AG23">
         <v>81</v>
       </c>
-      <c r="AG23">
+      <c r="AH23">
         <v>88</v>
       </c>
-      <c r="AH23">
+      <c r="AI23">
         <v>20</v>
       </c>
-      <c r="AI23">
+      <c r="AJ23">
         <v>162</v>
       </c>
-      <c r="AJ23">
+      <c r="AK23">
         <v>7</v>
       </c>
-      <c r="AK23">
+      <c r="AL23">
         <v>91</v>
       </c>
-      <c r="AL23">
+      <c r="AM23">
         <v>48</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24">
-        <v>0</v>
+    <row r="24" spans="1:39">
+      <c r="A24" t="s">
+        <v>50</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3127,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -3169,54 +7240,57 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
         <v>3043</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>246</v>
       </c>
-      <c r="AD24">
+      <c r="AE24">
         <v>2.565</v>
       </c>
-      <c r="AE24">
+      <c r="AF24">
         <v>2880</v>
       </c>
-      <c r="AF24">
+      <c r="AG24">
         <v>81</v>
       </c>
-      <c r="AG24">
+      <c r="AH24">
         <v>97</v>
       </c>
-      <c r="AH24">
+      <c r="AI24">
         <v>260</v>
       </c>
-      <c r="AI24">
+      <c r="AJ24">
         <v>350</v>
       </c>
-      <c r="AJ24">
+      <c r="AK24">
         <v>115</v>
       </c>
-      <c r="AK24">
+      <c r="AL24">
         <v>63</v>
       </c>
-      <c r="AL24">
+      <c r="AM24">
         <v>164</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25">
-        <v>0</v>
+    <row r="25" spans="1:39">
+      <c r="A25" t="s">
+        <v>51</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3234,28 +7308,28 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -3264,10 +7338,10 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -3282,57 +7356,60 @@
         <v>0</v>
       </c>
       <c r="W25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X25">
         <v>2</v>
       </c>
       <c r="Y25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
         <v>3147</v>
       </c>
-      <c r="AC25">
+      <c r="AD25">
         <v>241</v>
       </c>
-      <c r="AD25">
+      <c r="AE25">
         <v>1.386</v>
       </c>
-      <c r="AE25">
+      <c r="AF25">
         <v>2976</v>
       </c>
-      <c r="AF25">
+      <c r="AG25">
         <v>80</v>
       </c>
-      <c r="AG25">
+      <c r="AH25">
         <v>99</v>
       </c>
-      <c r="AH25">
+      <c r="AI25">
         <v>140</v>
       </c>
-      <c r="AI25">
+      <c r="AJ25">
         <v>250</v>
       </c>
-      <c r="AJ25">
+      <c r="AK25">
         <v>60</v>
       </c>
-      <c r="AK25">
+      <c r="AL25">
         <v>52</v>
       </c>
-      <c r="AL25">
+      <c r="AM25">
         <v>123</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26">
-        <v>0</v>
+    <row r="26" spans="1:39">
+      <c r="A26" t="s">
+        <v>52</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3356,25 +7433,25 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -3383,10 +7460,10 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -3398,57 +7475,60 @@
         <v>0</v>
       </c>
       <c r="W26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
         <v>3278</v>
       </c>
-      <c r="AC26">
+      <c r="AD26">
         <v>231</v>
       </c>
-      <c r="AD26">
+      <c r="AE26">
         <v>1.792</v>
       </c>
-      <c r="AE26">
+      <c r="AF26">
         <v>3870</v>
       </c>
-      <c r="AF26">
+      <c r="AG26">
         <v>79</v>
       </c>
-      <c r="AG26">
+      <c r="AH26">
         <v>100</v>
       </c>
-      <c r="AH26">
+      <c r="AI26">
         <v>422</v>
       </c>
-      <c r="AI26">
+      <c r="AJ26">
         <v>620</v>
       </c>
-      <c r="AJ26">
+      <c r="AK26">
         <v>180</v>
       </c>
-      <c r="AK26">
+      <c r="AL26">
         <v>41</v>
       </c>
-      <c r="AL26">
+      <c r="AM26">
         <v>167</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27">
-        <v>0</v>
+    <row r="27" spans="1:39">
+      <c r="A27" t="s">
+        <v>53</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3457,114 +7537,117 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <v>2</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q27">
         <v>2</v>
       </c>
       <c r="R27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S27">
         <v>1</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X27">
         <v>4</v>
       </c>
       <c r="Y27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB27">
+        <v>2</v>
+      </c>
+      <c r="AC27">
         <v>3579</v>
       </c>
-      <c r="AC27">
+      <c r="AD27">
         <v>214</v>
       </c>
-      <c r="AD27">
+      <c r="AE27">
         <v>1.792</v>
       </c>
-      <c r="AE27">
+      <c r="AF27">
         <v>3910</v>
       </c>
-      <c r="AF27">
+      <c r="AG27">
         <v>79</v>
       </c>
-      <c r="AG27">
+      <c r="AH27">
         <v>94</v>
       </c>
-      <c r="AH27">
+      <c r="AI27">
         <v>143</v>
       </c>
-      <c r="AI27">
+      <c r="AJ27">
         <v>300</v>
       </c>
-      <c r="AJ27">
+      <c r="AK27">
         <v>30</v>
       </c>
-      <c r="AK27">
+      <c r="AL27">
         <v>62</v>
       </c>
-      <c r="AL27">
+      <c r="AM27">
         <v>89</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28">
-        <v>0</v>
+    <row r="28" spans="1:39">
+      <c r="A28" t="s">
+        <v>54</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3573,114 +7656,117 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N28">
         <v>4</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q28">
         <v>3</v>
       </c>
       <c r="R28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X28">
         <v>5</v>
       </c>
       <c r="Y28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB28">
+        <v>3</v>
+      </c>
+      <c r="AC28">
         <v>3732</v>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <v>206</v>
       </c>
-      <c r="AD28">
+      <c r="AE28">
         <v>2.565</v>
       </c>
-      <c r="AE28">
+      <c r="AF28">
         <v>3960</v>
       </c>
-      <c r="AF28">
+      <c r="AG28">
         <v>81</v>
       </c>
-      <c r="AG28">
+      <c r="AH28">
         <v>90</v>
       </c>
-      <c r="AH28">
+      <c r="AI28">
         <v>58</v>
       </c>
-      <c r="AI28">
+      <c r="AJ28">
         <v>300</v>
       </c>
-      <c r="AJ28">
+      <c r="AK28">
         <v>26</v>
       </c>
-      <c r="AK28">
+      <c r="AL28">
         <v>72</v>
       </c>
-      <c r="AL28">
+      <c r="AM28">
         <v>63</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29">
-        <v>0</v>
+    <row r="29" spans="1:39">
+      <c r="A29" t="s">
+        <v>55</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3689,64 +7775,64 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>1</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q29">
         <v>4</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T29">
         <v>4</v>
       </c>
       <c r="U29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V29">
         <v>3</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -3758,48 +7844,51 @@
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB29">
+        <v>4</v>
+      </c>
+      <c r="AC29">
         <v>3947</v>
       </c>
-      <c r="AC29">
+      <c r="AD29">
         <v>195</v>
       </c>
-      <c r="AD29">
+      <c r="AE29">
         <v>1.386</v>
       </c>
-      <c r="AE29">
+      <c r="AF29">
         <v>4320</v>
       </c>
-      <c r="AF29">
+      <c r="AG29">
         <v>83</v>
       </c>
-      <c r="AG29">
+      <c r="AH29">
         <v>100</v>
       </c>
-      <c r="AH29">
+      <c r="AI29">
         <v>74</v>
       </c>
-      <c r="AI29">
+      <c r="AJ29">
         <v>400</v>
       </c>
-      <c r="AJ29">
+      <c r="AK29">
         <v>30</v>
       </c>
-      <c r="AK29">
+      <c r="AL29">
         <v>81</v>
       </c>
-      <c r="AL29">
+      <c r="AM29">
         <v>45</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30">
-        <v>0</v>
+    <row r="30" spans="1:39">
+      <c r="A30" t="s">
+        <v>56</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -3814,105 +7903,108 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>2</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <v>5</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T30">
         <v>3</v>
       </c>
       <c r="U30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V30">
         <v>4</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X30">
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB30">
+        <v>4</v>
+      </c>
+      <c r="AC30">
         <v>4220</v>
       </c>
-      <c r="AC30">
+      <c r="AD30">
         <v>183</v>
       </c>
-      <c r="AD30">
+      <c r="AE30">
         <v>1.946</v>
       </c>
-      <c r="AE30">
+      <c r="AF30">
         <v>6770</v>
       </c>
-      <c r="AF30">
+      <c r="AG30">
         <v>78</v>
       </c>
-      <c r="AG30">
+      <c r="AH30">
         <v>110</v>
       </c>
-      <c r="AH30">
+      <c r="AI30">
         <v>45</v>
       </c>
-      <c r="AI30">
+      <c r="AJ30">
         <v>162</v>
       </c>
-      <c r="AJ30">
+      <c r="AK30">
         <v>10</v>
       </c>
-      <c r="AK30">
+      <c r="AL30">
         <v>90</v>
       </c>
-      <c r="AL30">
+      <c r="AM30">
         <v>42</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31">
-        <v>0</v>
+    <row r="31" spans="1:39">
+      <c r="A31" t="s">
+        <v>57</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3930,13 +8022,13 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31">
         <v>3</v>
@@ -3945,25 +8037,25 @@
         <v>3</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M31">
         <v>5</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P31">
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S31">
         <v>5</v>
@@ -3993,36 +8085,39 @@
         <v>5</v>
       </c>
       <c r="AB31">
+        <v>5</v>
+      </c>
+      <c r="AC31">
         <v>4530</v>
       </c>
-      <c r="AC31">
+      <c r="AD31">
         <v>172</v>
       </c>
-      <c r="AD31">
+      <c r="AE31">
         <v>1.099</v>
       </c>
-      <c r="AE31">
+      <c r="AF31">
         <v>6900</v>
       </c>
-      <c r="AF31">
+      <c r="AG31">
         <v>82</v>
       </c>
-      <c r="AG31">
+      <c r="AH31">
         <v>109</v>
       </c>
-      <c r="AH31">
+      <c r="AI31">
         <v>65</v>
       </c>
-      <c r="AI31">
+      <c r="AJ31">
         <v>160</v>
       </c>
-      <c r="AJ31">
+      <c r="AK31">
         <v>10</v>
       </c>
-      <c r="AK31">
+      <c r="AL31">
         <v>82</v>
       </c>
-      <c r="AL31">
+      <c r="AM31">
         <v>44</v>
       </c>
     </row>
